--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40201/BU03/HRM/pre LAM_HRM-2031-0400/Panel 7/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU03_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.91687</v>
+        <v>17.13405</v>
       </c>
       <c r="D2" t="n">
-        <v>16.67792</v>
+        <v>16.85222</v>
       </c>
       <c r="E2" t="n">
-        <v>16.2878</v>
+        <v>16.95134</v>
       </c>
       <c r="F2" t="n">
-        <v>43.479</v>
+        <v>41.56742</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0512</v>
+        <v>0.05068</v>
       </c>
       <c r="H2" t="n">
-        <v>1.86168</v>
+        <v>1.81127</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.53495</v>
+        <v>16.86415</v>
       </c>
       <c r="D3" t="n">
-        <v>16.19695</v>
+        <v>16.45685</v>
       </c>
       <c r="E3" t="n">
-        <v>16.78038</v>
+        <v>16.60064</v>
       </c>
       <c r="F3" t="n">
-        <v>42.34092</v>
+        <v>42.43932</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05166</v>
+        <v>0.05111</v>
       </c>
       <c r="H3" t="n">
-        <v>1.84436</v>
+        <v>1.83607</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.63747</v>
+        <v>17.22708</v>
       </c>
       <c r="D4" t="n">
-        <v>16.34915</v>
+        <v>16.8165</v>
       </c>
       <c r="E4" t="n">
-        <v>16.52851</v>
+        <v>16.9121</v>
       </c>
       <c r="F4" t="n">
-        <v>42.48925</v>
+        <v>43.07429</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05077</v>
+        <v>0.0502</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81484</v>
+        <v>1.8114</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.91424</v>
+        <v>16.81646</v>
       </c>
       <c r="D5" t="n">
-        <v>16.83773</v>
+        <v>16.62118</v>
       </c>
       <c r="E5" t="n">
-        <v>16.85794</v>
+        <v>16.80697</v>
       </c>
       <c r="F5" t="n">
-        <v>42.88128</v>
+        <v>42.40799</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05082</v>
+        <v>0.05066</v>
       </c>
       <c r="H5" t="n">
-        <v>1.82517</v>
+        <v>1.83542</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.8568</v>
+        <v>16.83809</v>
       </c>
       <c r="D6" t="n">
-        <v>16.2442</v>
+        <v>16.68178</v>
       </c>
       <c r="E6" t="n">
-        <v>16.5059</v>
+        <v>16.7773</v>
       </c>
       <c r="F6" t="n">
-        <v>42.4039</v>
+        <v>43.13894</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05076</v>
+        <v>0.04963</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83554</v>
+        <v>1.84642</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.07382</v>
+        <v>16.85468</v>
       </c>
       <c r="D7" t="n">
-        <v>17.11348</v>
+        <v>16.58464</v>
       </c>
       <c r="E7" t="n">
-        <v>16.618</v>
+        <v>16.61603</v>
       </c>
       <c r="F7" t="n">
-        <v>42.55313</v>
+        <v>42.35806</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05026</v>
+        <v>0.05029</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85314</v>
+        <v>1.84347</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.83812</v>
+        <v>17.59993</v>
       </c>
       <c r="D8" t="n">
-        <v>16.89925</v>
+        <v>16.77493</v>
       </c>
       <c r="E8" t="n">
-        <v>16.81269</v>
+        <v>16.83925</v>
       </c>
       <c r="F8" t="n">
-        <v>42.55829</v>
+        <v>43.31014</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05013</v>
+        <v>0.05134</v>
       </c>
       <c r="H8" t="n">
-        <v>1.84572</v>
+        <v>1.82545</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.73061</v>
+        <v>16.96806</v>
       </c>
       <c r="D9" t="n">
-        <v>16.79323</v>
+        <v>16.59552</v>
       </c>
       <c r="E9" t="n">
-        <v>16.47022</v>
+        <v>16.70039</v>
       </c>
       <c r="F9" t="n">
-        <v>42.19667</v>
+        <v>42.93254</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05084</v>
+        <v>0.05137</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81957</v>
+        <v>1.81364</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.1977</v>
+        <v>17.06091</v>
       </c>
       <c r="D10" t="n">
-        <v>16.4716</v>
+        <v>16.76528</v>
       </c>
       <c r="E10" t="n">
-        <v>16.6772</v>
+        <v>16.84044</v>
       </c>
       <c r="F10" t="n">
-        <v>42.28831</v>
+        <v>42.44416</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05092</v>
+        <v>0.05214</v>
       </c>
       <c r="H10" t="n">
-        <v>1.82745</v>
+        <v>1.81042</v>
       </c>
     </row>
     <row r="11">
@@ -722,22 +722,22 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16.59989</v>
+        <v>16.8074</v>
       </c>
       <c r="D12" t="n">
-        <v>16.47501</v>
+        <v>16.67465</v>
       </c>
       <c r="E12" t="n">
-        <v>16.67377</v>
+        <v>16.78658</v>
       </c>
       <c r="F12" t="n">
-        <v>42.65355</v>
+        <v>42.68935</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05045</v>
+        <v>0.05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.83742</v>
+        <v>1.8003</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>16.85644</v>
+        <v>17.1163</v>
       </c>
       <c r="D13" t="n">
-        <v>16.50646</v>
+        <v>16.67538</v>
       </c>
       <c r="E13" t="n">
-        <v>16.58716</v>
+        <v>17.10659</v>
       </c>
       <c r="F13" t="n">
-        <v>43.17405</v>
+        <v>43.01252</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05127</v>
+        <v>0.05071</v>
       </c>
       <c r="H13" t="n">
-        <v>1.84213</v>
+        <v>1.84166</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>16.86642</v>
+        <v>17.19692</v>
       </c>
       <c r="D14" t="n">
-        <v>16.54701</v>
+        <v>16.75402</v>
       </c>
       <c r="E14" t="n">
-        <v>17.25127</v>
+        <v>16.76983</v>
       </c>
       <c r="F14" t="n">
-        <v>42.2267</v>
+        <v>42.69005</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05102</v>
+        <v>0.05138</v>
       </c>
       <c r="H14" t="n">
-        <v>1.82798</v>
+        <v>1.81654</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>16.98305</v>
+        <v>16.93742</v>
       </c>
       <c r="D15" t="n">
-        <v>16.90449</v>
+        <v>16.43184</v>
       </c>
       <c r="E15" t="n">
-        <v>17.22628</v>
+        <v>16.69371</v>
       </c>
       <c r="F15" t="n">
-        <v>42.81876</v>
+        <v>43.06889</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05019</v>
+        <v>0.05055</v>
       </c>
       <c r="H15" t="n">
-        <v>1.82208</v>
+        <v>1.83064</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>16.75274</v>
+        <v>16.98335</v>
       </c>
       <c r="D16" t="n">
-        <v>16.76233</v>
+        <v>16.82007</v>
       </c>
       <c r="E16" t="n">
-        <v>16.90952</v>
+        <v>16.94739</v>
       </c>
       <c r="F16" t="n">
-        <v>43.39981</v>
+        <v>41.60284</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05098</v>
+        <v>0.05076</v>
       </c>
       <c r="H16" t="n">
-        <v>1.78948</v>
+        <v>1.84565</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.06332</v>
+        <v>16.98507</v>
       </c>
       <c r="D17" t="n">
-        <v>16.81057</v>
+        <v>16.68345</v>
       </c>
       <c r="E17" t="n">
-        <v>16.76661</v>
+        <v>16.69475</v>
       </c>
       <c r="F17" t="n">
-        <v>42.12015</v>
+        <v>43.38665</v>
       </c>
       <c r="G17" t="n">
-        <v>0.0518</v>
+        <v>0.05117</v>
       </c>
       <c r="H17" t="n">
-        <v>1.79323</v>
+        <v>1.86204</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>16.88038</v>
+        <v>17.00178</v>
       </c>
       <c r="D18" t="n">
-        <v>16.66685</v>
+        <v>16.57554</v>
       </c>
       <c r="E18" t="n">
-        <v>16.41343</v>
+        <v>16.58284</v>
       </c>
       <c r="F18" t="n">
-        <v>42.93832</v>
+        <v>43.67551</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05153</v>
+        <v>0.05042</v>
       </c>
       <c r="H18" t="n">
-        <v>1.81896</v>
+        <v>1.82135</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.79275</v>
+        <v>17.04394</v>
       </c>
       <c r="D19" t="n">
-        <v>16.98198</v>
+        <v>16.56102</v>
       </c>
       <c r="E19" t="n">
-        <v>17.04133</v>
+        <v>16.57046</v>
       </c>
       <c r="F19" t="n">
-        <v>43.34307</v>
+        <v>42.87327</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05072</v>
+        <v>0.05201</v>
       </c>
       <c r="H19" t="n">
-        <v>1.85598</v>
+        <v>1.84441</v>
       </c>
     </row>
     <row r="20">
@@ -922,22 +922,22 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.12362</v>
+        <v>16.85894</v>
       </c>
       <c r="D20" t="n">
-        <v>16.6691</v>
+        <v>16.56102</v>
       </c>
       <c r="E20" t="n">
-        <v>16.7094</v>
+        <v>16.72484</v>
       </c>
       <c r="F20" t="n">
-        <v>42.569</v>
+        <v>43.48077</v>
       </c>
       <c r="G20" t="n">
-        <v>0.05</v>
+        <v>0.05186</v>
       </c>
       <c r="H20" t="n">
-        <v>1.8704</v>
+        <v>1.80803</v>
       </c>
     </row>
     <row r="21">
@@ -974,16 +974,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.72427</v>
+        <v>15.55221</v>
       </c>
       <c r="D22" t="n">
-        <v>15.85918</v>
+        <v>15.46023</v>
       </c>
       <c r="E22" t="n">
-        <v>15.76934</v>
+        <v>15.50309</v>
       </c>
       <c r="F22" t="n">
-        <v>248.799</v>
+        <v>252.23961</v>
       </c>
     </row>
     <row r="23">
@@ -993,16 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.81242</v>
+        <v>15.88119</v>
       </c>
       <c r="D23" t="n">
-        <v>15.80938</v>
+        <v>15.65696</v>
       </c>
       <c r="E23" t="n">
-        <v>15.45584</v>
+        <v>15.68948</v>
       </c>
       <c r="F23" t="n">
-        <v>255.64962</v>
+        <v>253.08495</v>
       </c>
     </row>
     <row r="24">
@@ -1012,16 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.90005</v>
+        <v>16.03087</v>
       </c>
       <c r="D24" t="n">
-        <v>16.05051</v>
+        <v>15.63692</v>
       </c>
       <c r="E24" t="n">
-        <v>15.72572</v>
+        <v>15.96221</v>
       </c>
       <c r="F24" t="n">
-        <v>253.8089</v>
+        <v>256.41606</v>
       </c>
     </row>
     <row r="25">
@@ -1031,16 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.48831</v>
+        <v>15.93735</v>
       </c>
       <c r="D25" t="n">
-        <v>15.69987</v>
+        <v>15.3487</v>
       </c>
       <c r="E25" t="n">
-        <v>15.59065</v>
+        <v>15.61846</v>
       </c>
       <c r="F25" t="n">
-        <v>256.54006</v>
+        <v>256.67488</v>
       </c>
     </row>
     <row r="26">
@@ -1050,16 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>15.80453</v>
+        <v>15.90779</v>
       </c>
       <c r="D26" t="n">
-        <v>15.35928</v>
+        <v>15.64479</v>
       </c>
       <c r="E26" t="n">
-        <v>15.62947</v>
+        <v>15.78977</v>
       </c>
       <c r="F26" t="n">
-        <v>250.85608</v>
+        <v>261.30255</v>
       </c>
     </row>
     <row r="27">
@@ -1069,16 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>15.69058</v>
+        <v>16.07205</v>
       </c>
       <c r="D27" t="n">
-        <v>15.57923</v>
+        <v>15.37786</v>
       </c>
       <c r="E27" t="n">
-        <v>15.80766</v>
+        <v>15.68058</v>
       </c>
       <c r="F27" t="n">
-        <v>255.79863</v>
+        <v>254.80116</v>
       </c>
     </row>
     <row r="28">
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>15.76675</v>
+        <v>15.99237</v>
       </c>
       <c r="D28" t="n">
-        <v>15.58069</v>
+        <v>15.56573</v>
       </c>
       <c r="E28" t="n">
-        <v>15.79493</v>
+        <v>15.813</v>
       </c>
       <c r="F28" t="n">
-        <v>249.32788</v>
+        <v>257.42477</v>
       </c>
     </row>
     <row r="29">
@@ -1107,16 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>15.70888</v>
+        <v>15.8556</v>
       </c>
       <c r="D29" t="n">
-        <v>15.71392</v>
+        <v>15.4963</v>
       </c>
       <c r="E29" t="n">
-        <v>15.74114</v>
+        <v>15.6116</v>
       </c>
       <c r="F29" t="n">
-        <v>254.33215</v>
+        <v>250.57253</v>
       </c>
     </row>
     <row r="30">
@@ -1126,16 +1126,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>15.59341</v>
+        <v>16.09887</v>
       </c>
       <c r="D30" t="n">
-        <v>15.80032</v>
+        <v>15.57739</v>
       </c>
       <c r="E30" t="n">
-        <v>15.82199</v>
+        <v>15.59926</v>
       </c>
       <c r="F30" t="n">
-        <v>258.60289</v>
+        <v>257.63724</v>
       </c>
     </row>
     <row r="31">
@@ -1177,19 +1177,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>17.0681</v>
+        <v>16.82747</v>
       </c>
       <c r="D32" t="n">
-        <v>16.05923</v>
+        <v>16.07635</v>
       </c>
       <c r="E32" t="n">
-        <v>16.53255</v>
+        <v>16.1619</v>
       </c>
       <c r="F32" t="n">
-        <v>21.77097</v>
+        <v>21.61029</v>
       </c>
       <c r="G32" t="n">
-        <v>34.30464</v>
+        <v>33.86066</v>
       </c>
     </row>
     <row r="33">
@@ -1199,19 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>16.92152</v>
+        <v>16.69652</v>
       </c>
       <c r="D33" t="n">
-        <v>16.37879</v>
+        <v>15.85877</v>
       </c>
       <c r="E33" t="n">
-        <v>16.73028</v>
+        <v>16.54256</v>
       </c>
       <c r="F33" t="n">
-        <v>22.3608</v>
+        <v>21.68853</v>
       </c>
       <c r="G33" t="n">
-        <v>34.29055</v>
+        <v>34.14378</v>
       </c>
     </row>
     <row r="34">
@@ -1221,19 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.61438</v>
+        <v>16.55587</v>
       </c>
       <c r="D34" t="n">
-        <v>16.14318</v>
+        <v>15.92039</v>
       </c>
       <c r="E34" t="n">
-        <v>16.72891</v>
+        <v>16.22579</v>
       </c>
       <c r="F34" t="n">
-        <v>21.87649</v>
+        <v>21.66635</v>
       </c>
       <c r="G34" t="n">
-        <v>34.31607</v>
+        <v>34.68908</v>
       </c>
     </row>
     <row r="35">
@@ -1243,19 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>16.54417</v>
+        <v>16.57543</v>
       </c>
       <c r="D35" t="n">
-        <v>16.06527</v>
+        <v>15.78586</v>
       </c>
       <c r="E35" t="n">
-        <v>16.37276</v>
+        <v>16.35574</v>
       </c>
       <c r="F35" t="n">
-        <v>21.65134</v>
+        <v>22.14584</v>
       </c>
       <c r="G35" t="n">
-        <v>33.74688</v>
+        <v>34.64581</v>
       </c>
     </row>
     <row r="36">
@@ -1265,19 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>16.45007</v>
+        <v>16.65523</v>
       </c>
       <c r="D36" t="n">
-        <v>16.10918</v>
+        <v>16.25942</v>
       </c>
       <c r="E36" t="n">
-        <v>16.49463</v>
+        <v>16.50799</v>
       </c>
       <c r="F36" t="n">
-        <v>21.87788</v>
+        <v>21.68683</v>
       </c>
       <c r="G36" t="n">
-        <v>34.89549</v>
+        <v>34.50577</v>
       </c>
     </row>
     <row r="37">
@@ -1287,19 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>16.76936</v>
+        <v>16.59887</v>
       </c>
       <c r="D37" t="n">
-        <v>15.73708</v>
+        <v>16.15131</v>
       </c>
       <c r="E37" t="n">
-        <v>16.22294</v>
+        <v>16.31915</v>
       </c>
       <c r="F37" t="n">
-        <v>21.65546</v>
+        <v>22.42109</v>
       </c>
       <c r="G37" t="n">
-        <v>33.66799</v>
+        <v>35.23195</v>
       </c>
     </row>
     <row r="38">
@@ -1309,19 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>16.7414</v>
+        <v>16.54731</v>
       </c>
       <c r="D38" t="n">
-        <v>15.90755</v>
+        <v>16.11808</v>
       </c>
       <c r="E38" t="n">
-        <v>16.38732</v>
+        <v>16.40755</v>
       </c>
       <c r="F38" t="n">
-        <v>21.84044</v>
+        <v>21.95145</v>
       </c>
       <c r="G38" t="n">
-        <v>34.55884</v>
+        <v>33.71076</v>
       </c>
     </row>
     <row r="39">
@@ -1331,19 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.38581</v>
+        <v>16.75349</v>
       </c>
       <c r="D39" t="n">
-        <v>16.38932</v>
+        <v>15.81419</v>
       </c>
       <c r="E39" t="n">
-        <v>16.5098</v>
+        <v>16.26356</v>
       </c>
       <c r="F39" t="n">
-        <v>22.08081</v>
+        <v>21.8922</v>
       </c>
       <c r="G39" t="n">
-        <v>33.85901</v>
+        <v>34.06978</v>
       </c>
     </row>
     <row r="40">
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>16.66954</v>
+        <v>16.58391</v>
       </c>
       <c r="D40" t="n">
-        <v>15.80767</v>
+        <v>16.10524</v>
       </c>
       <c r="E40" t="n">
-        <v>16.30404</v>
+        <v>16.24612</v>
       </c>
       <c r="F40" t="n">
-        <v>21.87699</v>
+        <v>22.63471</v>
       </c>
       <c r="G40" t="n">
-        <v>34.78912</v>
+        <v>33.71993</v>
       </c>
     </row>
     <row r="41">
@@ -1407,19 +1407,19 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>16.56475</v>
+        <v>16.82466</v>
       </c>
       <c r="D42" t="n">
-        <v>15.94052</v>
+        <v>16.0752</v>
       </c>
       <c r="E42" t="n">
-        <v>16.47272</v>
+        <v>16.60518</v>
       </c>
       <c r="F42" t="n">
-        <v>21.69922</v>
+        <v>21.81509</v>
       </c>
       <c r="G42" t="n">
-        <v>34.79449</v>
+        <v>34.10013</v>
       </c>
     </row>
     <row r="43">
@@ -1429,19 +1429,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>16.57152</v>
+        <v>16.67602</v>
       </c>
       <c r="D43" t="n">
-        <v>16.25953</v>
+        <v>16.27471</v>
       </c>
       <c r="E43" t="n">
-        <v>16.59585</v>
+        <v>16.45899</v>
       </c>
       <c r="F43" t="n">
-        <v>22.20163</v>
+        <v>21.4759</v>
       </c>
       <c r="G43" t="n">
-        <v>34.19717</v>
+        <v>34.42845</v>
       </c>
     </row>
     <row r="44">
@@ -1451,19 +1451,19 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>16.78862</v>
+        <v>16.64311</v>
       </c>
       <c r="D44" t="n">
-        <v>16.09526</v>
+        <v>16.1465</v>
       </c>
       <c r="E44" t="n">
-        <v>16.19927</v>
+        <v>16.5275</v>
       </c>
       <c r="F44" t="n">
-        <v>21.58788</v>
+        <v>21.5946</v>
       </c>
       <c r="G44" t="n">
-        <v>34.82555</v>
+        <v>34.71284</v>
       </c>
     </row>
     <row r="45">
@@ -1473,19 +1473,19 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>16.76146</v>
+        <v>17.00799</v>
       </c>
       <c r="D45" t="n">
-        <v>15.99566</v>
+        <v>16.21455</v>
       </c>
       <c r="E45" t="n">
-        <v>17.04534</v>
+        <v>16.80487</v>
       </c>
       <c r="F45" t="n">
-        <v>22.30463</v>
+        <v>21.93013</v>
       </c>
       <c r="G45" t="n">
-        <v>35.22519</v>
+        <v>34.01695</v>
       </c>
     </row>
     <row r="46">
@@ -1495,19 +1495,19 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>16.58113</v>
+        <v>16.91258</v>
       </c>
       <c r="D46" t="n">
-        <v>16.04902</v>
+        <v>15.63396</v>
       </c>
       <c r="E46" t="n">
-        <v>16.36868</v>
+        <v>16.8049</v>
       </c>
       <c r="F46" t="n">
-        <v>21.90511</v>
+        <v>22.00943</v>
       </c>
       <c r="G46" t="n">
-        <v>34.35818</v>
+        <v>35.2396</v>
       </c>
     </row>
     <row r="47">
@@ -1517,19 +1517,19 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>16.5632</v>
+        <v>16.85496</v>
       </c>
       <c r="D47" t="n">
-        <v>16.30488</v>
+        <v>15.57949</v>
       </c>
       <c r="E47" t="n">
-        <v>16.70537</v>
+        <v>16.5183</v>
       </c>
       <c r="F47" t="n">
-        <v>21.66249</v>
+        <v>22.38574</v>
       </c>
       <c r="G47" t="n">
-        <v>35.02514</v>
+        <v>34.84699</v>
       </c>
     </row>
     <row r="48">
@@ -1539,19 +1539,19 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>16.67901</v>
+        <v>16.83045</v>
       </c>
       <c r="D48" t="n">
-        <v>16.50641</v>
+        <v>15.89085</v>
       </c>
       <c r="E48" t="n">
-        <v>16.48426</v>
+        <v>16.11489</v>
       </c>
       <c r="F48" t="n">
-        <v>21.75098</v>
+        <v>22.05227</v>
       </c>
       <c r="G48" t="n">
-        <v>34.28325</v>
+        <v>33.93135</v>
       </c>
     </row>
     <row r="49">
@@ -1561,19 +1561,19 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>17.07413</v>
+        <v>16.7588</v>
       </c>
       <c r="D49" t="n">
-        <v>16.1104</v>
+        <v>15.94657</v>
       </c>
       <c r="E49" t="n">
-        <v>16.58875</v>
+        <v>16.36504</v>
       </c>
       <c r="F49" t="n">
-        <v>22.10136</v>
+        <v>21.67116</v>
       </c>
       <c r="G49" t="n">
-        <v>34.27733</v>
+        <v>34.21851</v>
       </c>
     </row>
     <row r="50">
@@ -1583,19 +1583,19 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>16.77882</v>
+        <v>16.71412</v>
       </c>
       <c r="D50" t="n">
-        <v>16.33254</v>
+        <v>16.15514</v>
       </c>
       <c r="E50" t="n">
-        <v>16.40758</v>
+        <v>16.67093</v>
       </c>
       <c r="F50" t="n">
-        <v>21.60098</v>
+        <v>21.91773</v>
       </c>
       <c r="G50" t="n">
-        <v>34.22309</v>
+        <v>34.39079</v>
       </c>
     </row>
     <row r="51">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.60722</v>
+        <v>0.61526</v>
       </c>
       <c r="D52" t="n">
-        <v>1.12525</v>
+        <v>1.1159</v>
       </c>
     </row>
     <row r="53">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.60636</v>
+        <v>0.6134500000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>1.11206</v>
+        <v>1.13122</v>
       </c>
     </row>
     <row r="54">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.61783</v>
+        <v>0.61205</v>
       </c>
       <c r="D54" t="n">
-        <v>1.11762</v>
+        <v>1.13652</v>
       </c>
     </row>
     <row r="55">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.61097</v>
+        <v>0.61565</v>
       </c>
       <c r="D55" t="n">
-        <v>1.11827</v>
+        <v>1.11045</v>
       </c>
     </row>
     <row r="56">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.60967</v>
+        <v>0.60995</v>
       </c>
       <c r="D56" t="n">
-        <v>1.13989</v>
+        <v>1.11269</v>
       </c>
     </row>
     <row r="57">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.61043</v>
+        <v>0.61143</v>
       </c>
       <c r="D57" t="n">
-        <v>1.12199</v>
+        <v>1.11106</v>
       </c>
     </row>
     <row r="58">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.63092</v>
+        <v>0.60309</v>
       </c>
       <c r="D58" t="n">
-        <v>1.11045</v>
+        <v>1.10919</v>
       </c>
     </row>
     <row r="59">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.61932</v>
+        <v>0.61353</v>
       </c>
       <c r="D59" t="n">
-        <v>1.11506</v>
+        <v>1.11324</v>
       </c>
     </row>
     <row r="60">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.6093</v>
+        <v>0.61778</v>
       </c>
       <c r="D60" t="n">
-        <v>1.12428</v>
+        <v>1.13031</v>
       </c>
     </row>
     <row r="61">
@@ -1756,10 +1756,10 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.61693</v>
+        <v>0.60646</v>
       </c>
       <c r="D62" t="n">
-        <v>1.10891</v>
+        <v>1.12245</v>
       </c>
     </row>
     <row r="63">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>0.60577</v>
+        <v>0.60786</v>
       </c>
       <c r="D63" t="n">
-        <v>1.11087</v>
+        <v>1.11547</v>
       </c>
     </row>
     <row r="64">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.6009100000000001</v>
+        <v>0.61656</v>
       </c>
       <c r="D64" t="n">
-        <v>1.11996</v>
+        <v>1.132</v>
       </c>
     </row>
     <row r="65">
@@ -1795,10 +1795,10 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.61751</v>
+        <v>0.62049</v>
       </c>
       <c r="D65" t="n">
-        <v>1.11651</v>
+        <v>1.13266</v>
       </c>
     </row>
     <row r="66">
@@ -1808,10 +1808,10 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>0.6103</v>
+        <v>0.61232</v>
       </c>
       <c r="D66" t="n">
-        <v>1.10528</v>
+        <v>1.11094</v>
       </c>
     </row>
     <row r="67">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>0.60488</v>
+        <v>0.6001300000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>1.15382</v>
+        <v>1.10459</v>
       </c>
     </row>
     <row r="68">
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.6144500000000001</v>
+        <v>0.60104</v>
       </c>
       <c r="D68" t="n">
-        <v>1.11843</v>
+        <v>1.14047</v>
       </c>
     </row>
     <row r="69">
@@ -1847,10 +1847,10 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>0.60784</v>
+        <v>0.60891</v>
       </c>
       <c r="D69" t="n">
-        <v>1.11006</v>
+        <v>1.10085</v>
       </c>
     </row>
     <row r="70">
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>0.61755</v>
+        <v>0.61607</v>
       </c>
       <c r="D70" t="n">
-        <v>1.12661</v>
+        <v>1.09101</v>
       </c>
     </row>
     <row r="71">
@@ -1920,28 +1920,28 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0.7541600000000001</v>
+        <v>0.74678</v>
       </c>
       <c r="D72" t="n">
-        <v>0.08404</v>
+        <v>0.08297</v>
       </c>
       <c r="E72" t="n">
-        <v>0.6088</v>
+        <v>0.61673</v>
       </c>
       <c r="F72" t="n">
-        <v>0.9547099999999999</v>
+        <v>0.9726900000000001</v>
       </c>
       <c r="G72" t="n">
-        <v>0.10911</v>
+        <v>0.11256</v>
       </c>
       <c r="H72" t="n">
-        <v>0.00759</v>
+        <v>0.00751</v>
       </c>
       <c r="I72" t="n">
-        <v>0.09403</v>
+        <v>0.09553</v>
       </c>
       <c r="J72" t="n">
-        <v>0.12724</v>
+        <v>0.12885</v>
       </c>
     </row>
     <row r="73">
@@ -1951,28 +1951,28 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.7599</v>
+        <v>0.75514</v>
       </c>
       <c r="D73" t="n">
-        <v>0.08192000000000001</v>
+        <v>0.08180999999999999</v>
       </c>
       <c r="E73" t="n">
-        <v>0.61779</v>
+        <v>0.60802</v>
       </c>
       <c r="F73" t="n">
-        <v>0.96583</v>
+        <v>0.95743</v>
       </c>
       <c r="G73" t="n">
-        <v>0.11002</v>
+        <v>0.10865</v>
       </c>
       <c r="H73" t="n">
-        <v>0.00771</v>
+        <v>0.00744</v>
       </c>
       <c r="I73" t="n">
-        <v>0.09419</v>
+        <v>0.09291000000000001</v>
       </c>
       <c r="J73" t="n">
-        <v>0.12789</v>
+        <v>0.12602</v>
       </c>
     </row>
     <row r="74">
@@ -1982,28 +1982,28 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>0.7548899999999999</v>
+        <v>0.7471100000000001</v>
       </c>
       <c r="D74" t="n">
-        <v>0.07961</v>
+        <v>0.08208</v>
       </c>
       <c r="E74" t="n">
-        <v>0.61965</v>
+        <v>0.59927</v>
       </c>
       <c r="F74" t="n">
-        <v>0.96223</v>
+        <v>0.9614200000000001</v>
       </c>
       <c r="G74" t="n">
-        <v>0.10869</v>
+        <v>0.10953</v>
       </c>
       <c r="H74" t="n">
-        <v>0.00757</v>
+        <v>0.00763</v>
       </c>
       <c r="I74" t="n">
-        <v>0.09531000000000001</v>
+        <v>0.09433</v>
       </c>
       <c r="J74" t="n">
-        <v>0.12886</v>
+        <v>0.1265</v>
       </c>
     </row>
     <row r="75">
@@ -2013,28 +2013,28 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0.76952</v>
+        <v>0.7682</v>
       </c>
       <c r="D75" t="n">
-        <v>0.08132</v>
+        <v>0.08055</v>
       </c>
       <c r="E75" t="n">
-        <v>0.62113</v>
+        <v>0.61904</v>
       </c>
       <c r="F75" t="n">
-        <v>0.96071</v>
+        <v>0.99138</v>
       </c>
       <c r="G75" t="n">
-        <v>0.10965</v>
+        <v>0.10969</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0076</v>
+        <v>0.00757</v>
       </c>
       <c r="I75" t="n">
-        <v>0.09264</v>
+        <v>0.09399</v>
       </c>
       <c r="J75" t="n">
-        <v>0.12657</v>
+        <v>0.12799</v>
       </c>
     </row>
     <row r="76">
@@ -2044,28 +2044,28 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>0.7549400000000001</v>
+        <v>0.74826</v>
       </c>
       <c r="D76" t="n">
-        <v>0.08072</v>
+        <v>0.07943</v>
       </c>
       <c r="E76" t="n">
-        <v>0.61104</v>
+        <v>0.59706</v>
       </c>
       <c r="F76" t="n">
-        <v>0.96388</v>
+        <v>0.97263</v>
       </c>
       <c r="G76" t="n">
-        <v>0.11108</v>
+        <v>0.11036</v>
       </c>
       <c r="H76" t="n">
-        <v>0.00769</v>
+        <v>0.00771</v>
       </c>
       <c r="I76" t="n">
-        <v>0.09407</v>
+        <v>0.09344</v>
       </c>
       <c r="J76" t="n">
-        <v>0.12727</v>
+        <v>0.12751</v>
       </c>
     </row>
     <row r="77">
@@ -2075,28 +2075,28 @@
         </is>
       </c>
       <c r="C77" t="n">
-        <v>0.74703</v>
+        <v>0.73745</v>
       </c>
       <c r="D77" t="n">
-        <v>0.08207</v>
+        <v>0.08289000000000001</v>
       </c>
       <c r="E77" t="n">
-        <v>0.60926</v>
+        <v>0.6173999999999999</v>
       </c>
       <c r="F77" t="n">
-        <v>0.98616</v>
+        <v>0.95873</v>
       </c>
       <c r="G77" t="n">
-        <v>0.10842</v>
+        <v>0.1083</v>
       </c>
       <c r="H77" t="n">
-        <v>0.00761</v>
+        <v>0.00757</v>
       </c>
       <c r="I77" t="n">
-        <v>0.09318</v>
+        <v>0.09634</v>
       </c>
       <c r="J77" t="n">
-        <v>0.12694</v>
+        <v>0.12768</v>
       </c>
     </row>
     <row r="78">
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>0.7634</v>
+        <v>0.74513</v>
       </c>
       <c r="D78" t="n">
-        <v>0.08248999999999999</v>
+        <v>0.08042000000000001</v>
       </c>
       <c r="E78" t="n">
-        <v>0.62054</v>
+        <v>0.60256</v>
       </c>
       <c r="F78" t="n">
-        <v>0.99439</v>
+        <v>0.95019</v>
       </c>
       <c r="G78" t="n">
-        <v>0.11073</v>
+        <v>0.10997</v>
       </c>
       <c r="H78" t="n">
-        <v>0.00772</v>
+        <v>0.00751</v>
       </c>
       <c r="I78" t="n">
-        <v>0.09476999999999999</v>
+        <v>0.09353</v>
       </c>
       <c r="J78" t="n">
-        <v>0.12885</v>
+        <v>0.12647</v>
       </c>
     </row>
     <row r="79">
@@ -2137,28 +2137,28 @@
         </is>
       </c>
       <c r="C79" t="n">
-        <v>0.75037</v>
+        <v>0.7430099999999999</v>
       </c>
       <c r="D79" t="n">
-        <v>0.08162</v>
+        <v>0.08112999999999999</v>
       </c>
       <c r="E79" t="n">
-        <v>0.60619</v>
+        <v>0.60321</v>
       </c>
       <c r="F79" t="n">
-        <v>0.97437</v>
+        <v>0.98067</v>
       </c>
       <c r="G79" t="n">
-        <v>0.10942</v>
+        <v>0.11136</v>
       </c>
       <c r="H79" t="n">
-        <v>0.007889999999999999</v>
+        <v>0.0077</v>
       </c>
       <c r="I79" t="n">
-        <v>0.09549000000000001</v>
+        <v>0.09131</v>
       </c>
       <c r="J79" t="n">
-        <v>0.12775</v>
+        <v>0.12829</v>
       </c>
     </row>
     <row r="80">
@@ -2168,28 +2168,28 @@
         </is>
       </c>
       <c r="C80" t="n">
-        <v>0.76187</v>
+        <v>0.76001</v>
       </c>
       <c r="D80" t="n">
-        <v>0.08001</v>
+        <v>0.08175</v>
       </c>
       <c r="E80" t="n">
-        <v>0.60425</v>
+        <v>0.60202</v>
       </c>
       <c r="F80" t="n">
-        <v>0.97104</v>
+        <v>0.9627599999999999</v>
       </c>
       <c r="G80" t="n">
-        <v>0.11149</v>
+        <v>0.10878</v>
       </c>
       <c r="H80" t="n">
-        <v>0.00765</v>
+        <v>0.00756</v>
       </c>
       <c r="I80" t="n">
-        <v>0.09401</v>
+        <v>0.09493</v>
       </c>
       <c r="J80" t="n">
-        <v>0.12762</v>
+        <v>0.12755</v>
       </c>
     </row>
   </sheetData>
